--- a/outputs/32255.xlsx
+++ b/outputs/32255.xlsx
@@ -144,24 +144,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -361,272 +365,272 @@
   <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <f aca="false">IF(A2&lt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <f aca="false">IF(A2&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <f aca="false">IF(A2="","",IF(A2=0,1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <f aca="false">IF(A3&lt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <f aca="false">IF(A3&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <f aca="false">IF(A3="","",IF(A3=0,1,0))</f>
         <v>0</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <f aca="false">IF(A4&lt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <f aca="false">IF(A4&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <f aca="false">IF(A4="","",IF(A4=0,1,0))</f>
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="4" t="n">
         <f aca="false">SUM(C2:C13)</f>
         <v>1</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="4" t="n">
         <f aca="false">SUM(I4/I7%)</f>
         <v>12.5</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="5" t="n">
         <f aca="false">SUM(I4/I8%)</f>
         <v>14.2857142857143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <f aca="false">IF(A5&lt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <f aca="false">IF(A5&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <f aca="false">IF(A5="","",IF(A5=0,1,0))</f>
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <f aca="false">SUM(B2:B13)</f>
         <v>6</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="4" t="n">
         <f aca="false">SUM(I5/I7%)</f>
         <v>75</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <f aca="false">SUM(I5/I8%)</f>
         <v>85.7142857142857</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <f aca="false">IF(A6&lt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <f aca="false">IF(A6&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">IF(A6="","",IF(A6=0,1,0))</f>
         <v>0</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <f aca="false">SUM(D2:D13)</f>
         <v>1</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="4" t="n">
         <f aca="false">SUM(I6/I7%)</f>
         <v>12.5</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>0.79</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <f aca="false">IF(A7&lt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <f aca="false">IF(A7&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <f aca="false">IF(A7="","",IF(A7=0,1,0))</f>
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="4" t="n">
         <f aca="false">SUM(I4:I6)</f>
         <v>8</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="4" t="n">
         <f aca="false">SUM(J4:J6)</f>
         <v>100</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="5" t="n">
         <f aca="false">SUM(K4:K5)</f>
         <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="B8" s="0" t="n">
+      <c r="A8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="n">
         <f aca="false">IF(A8&lt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <f aca="false">IF(A8&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <f aca="false">IF(A8="","",IF(A8=0,1,0))</f>
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="4" t="n">
         <f aca="false">SUM(I4:I5)</f>
         <v>7</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <f aca="false">IF(A9&lt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <f aca="false">IF(A9&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <f aca="false">IF(A9="","",IF(A9=0,1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <f aca="false">IF(A10&lt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <f aca="false">IF(A10&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="0" t="str">
+      <c r="D10" s="1" t="str">
         <f aca="false">IF(A10="","",IF(A10=0,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <f aca="false">IF(A11&lt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <f aca="false">IF(A11&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="0" t="str">
+      <c r="D11" s="1" t="str">
         <f aca="false">IF(A11="","",IF(A11=0,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <f aca="false">IF(A12&lt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <f aca="false">IF(A12&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="0" t="str">
+      <c r="D12" s="1" t="str">
         <f aca="false">IF(A12="","",IF(A12=0,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <f aca="false">IF(A13&lt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <f aca="false">IF(A13&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="0" t="str">
+      <c r="D13" s="1" t="str">
         <f aca="false">IF(A13="","",IF(A13=0,1,0))</f>
         <v/>
       </c>
